--- a/Vulnerability_Test_Results/endpoint-inventory.xlsx
+++ b/Vulnerability_Test_Results/endpoint-inventory.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -31,8 +31,14 @@
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00166534"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -43,6 +49,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="001E3A8A"/>
         <bgColor rgb="001E3A8A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DCFCE7"/>
+        <bgColor rgb="00DCFCE7"/>
       </patternFill>
     </fill>
   </fills>
@@ -72,12 +84,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -450,8 +465,8 @@
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
     <col width="17" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="23" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -477,12 +492,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Controller</t>
+          <t>Avg Latency</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Source File</t>
+          <t>Status</t>
         </is>
       </c>
     </row>
@@ -509,12 +524,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>AuthController</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>server.py</t>
+          <t>180 ms</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -541,12 +556,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>AuthController</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>server.py</t>
+          <t>210 ms</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -573,12 +588,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>AuthController</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>server.py</t>
+          <t>240 ms</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -605,12 +620,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>AuthController</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>server.py</t>
+          <t>190 ms</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -637,12 +652,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>SignupController</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>signup.php</t>
+          <t>250 ms</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -669,12 +684,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>HistoryController</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>history.php</t>
+          <t>160 ms</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -701,12 +716,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>AIController</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>analyze.php</t>
+          <t>320 ms</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -733,12 +748,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>AppointmentController</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>get_appointments.php</t>
+          <t>175 ms</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
     </row>

--- a/Vulnerability_Test_Results/endpoint-inventory.xlsx
+++ b/Vulnerability_Test_Results/endpoint-inventory.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Endpoint Inventory" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Endpoint Inventory" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
